--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,1</t>
   </si>
   <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.0616,0.0871,0.0182,0.9355</t>
-  </si>
-  <si>
-    <t>0.0021,0.0033,0.0011,0.9976</t>
-  </si>
-  <si>
-    <t>0.0123,0.0339,0.0057,0.9844</t>
-  </si>
-  <si>
-    <t>0.0044,0.0024,0.0021,0.9961</t>
-  </si>
-  <si>
-    <t>0.9500,0.0170,0.0027,0.0259</t>
-  </si>
-  <si>
-    <t>0.9547,0.0127,0.0018,0.0229</t>
-  </si>
-  <si>
-    <t>0.9062,0.0663,0.0054,0.0266</t>
-  </si>
-  <si>
-    <t>0.9674,0.0135,0.0021,0.0121</t>
-  </si>
-  <si>
-    <t>0.9045,0.0552,0.0031,0.0255</t>
-  </si>
-  <si>
-    <t>0.9637,0.0139,0.0017,0.0169</t>
-  </si>
-  <si>
-    <t>0.9686,0.0133,0.0032,0.0133</t>
-  </si>
-  <si>
-    <t>0.9646,0.0086,0.0016,0.0208</t>
-  </si>
-  <si>
-    <t>0.1395,0.2859,0.0690,0.7280</t>
-  </si>
-  <si>
-    <t>0.0777,0.1026,0.8544,0.0591</t>
-  </si>
-  <si>
-    <t>0.1698,0.0238,0.8143,0.0363</t>
-  </si>
-  <si>
-    <t>0.2263,0.0632,0.7335,0.0456</t>
-  </si>
-  <si>
-    <t>0.6128,0.1658,0.2005,0.1058</t>
-  </si>
-  <si>
-    <t>0.0182,0.9734,0.0111,0.0186</t>
-  </si>
-  <si>
-    <t>0.0341,0.9587,0.0162,0.0205</t>
-  </si>
-  <si>
-    <t>0.0619,0.7636,0.0058,0.2455</t>
-  </si>
-  <si>
-    <t>0.0596,0.9211,0.0096,0.0400</t>
-  </si>
-  <si>
-    <t>0.0246,0.9665,0.0108,0.0245</t>
-  </si>
-  <si>
-    <t>0.0469,0.0254,0.5730,0.5301</t>
-  </si>
-  <si>
-    <t>0.0623,0.0183,0.1473,0.8426</t>
-  </si>
-  <si>
-    <t>0.0534,0.0160,0.8203,0.1729</t>
-  </si>
-  <si>
-    <t>0.2083,0.0353,0.5573,0.1974</t>
-  </si>
-  <si>
-    <t>0.0486,0.0157,0.8606,0.1468</t>
-  </si>
-  <si>
-    <t>0.0345,0.0106,0.8614,0.1406</t>
-  </si>
-  <si>
-    <t>0.0103,0.0108,0.9598,0.0717</t>
-  </si>
-  <si>
-    <t>0.0373,0.9118,0.0203,0.1688</t>
-  </si>
-  <si>
-    <t>0.6212,0.2207,0.1387,0.0618</t>
-  </si>
-  <si>
-    <t>0.0017,0.0116,0.9910,0.0394</t>
-  </si>
-  <si>
-    <t>0.0176,0.9452,0.2082,0.0062</t>
-  </si>
-  <si>
-    <t>0.3943,0.1066,0.0106,0.4532</t>
-  </si>
-  <si>
-    <t>0.3752,0.3359,0.1160,0.3080</t>
-  </si>
-  <si>
-    <t>0.7210,0.2614,0.0090,0.0352</t>
-  </si>
-  <si>
-    <t>0.1162,0.8628,0.1003,0.0417</t>
-  </si>
-  <si>
-    <t>0.0153,0.3764,0.8967,0.0224</t>
-  </si>
-  <si>
-    <t>0.0089,0.0180,0.8341,0.3223</t>
-  </si>
-  <si>
-    <t>0.0522,0.1198,0.7835,0.1636</t>
-  </si>
-  <si>
-    <t>0.0241,0.0079,0.5719,0.5611</t>
-  </si>
-  <si>
-    <t>0.0200,0.2991,0.9429,0.0089</t>
-  </si>
-  <si>
-    <t>0.0241,0.9184,0.3812,0.0116</t>
-  </si>
-  <si>
-    <t>0.0070,0.0168,0.9135,0.1822</t>
-  </si>
-  <si>
-    <t>0.0290,0.1913,0.0192,0.9422</t>
-  </si>
-  <si>
-    <t>0.0067,0.9187,0.0208,0.3850</t>
-  </si>
-  <si>
-    <t>0.0219,0.9068,0.1326,0.1467</t>
-  </si>
-  <si>
-    <t>0.0041,0.9794,0.0400,0.0596</t>
-  </si>
-  <si>
-    <t>0.0033,0.0339,0.9825,0.0274</t>
-  </si>
-  <si>
-    <t>0.0049,0.0531,0.9878,0.0101</t>
-  </si>
-  <si>
-    <t>0.0144,0.0107,0.9226,0.1318</t>
-  </si>
-  <si>
-    <t>0.0632,0.0110,0.8009,0.1485</t>
-  </si>
-  <si>
-    <t>0.0088,0.0424,0.9394,0.1047</t>
-  </si>
-  <si>
-    <t>0.0083,0.0409,0.9609,0.0496</t>
-  </si>
-  <si>
-    <t>0.9214,0.0474,0.0048,0.0219</t>
-  </si>
-  <si>
-    <t>0.8470,0.0430,0.0127,0.0830</t>
-  </si>
-  <si>
-    <t>0.8567,0.0334,0.0092,0.0978</t>
-  </si>
-  <si>
-    <t>0.0029,0.0187,0.9822,0.0764</t>
-  </si>
-  <si>
-    <t>0.9446,0.0113,0.0028,0.0426</t>
-  </si>
-  <si>
-    <t>0.9516,0.0127,0.0026,0.0274</t>
-  </si>
-  <si>
-    <t>0.9288,0.0357,0.0054,0.0305</t>
-  </si>
-  <si>
-    <t>0.0029,0.8842,0.9525,0.0006</t>
-  </si>
-  <si>
-    <t>0.0017,0.0189,0.9665,0.0948</t>
-  </si>
-  <si>
-    <t>0.0021,0.0088,0.9857,0.0384</t>
-  </si>
-  <si>
-    <t>0.0079,0.7120,0.9464,0.0019</t>
-  </si>
-  <si>
-    <t>0.0011,0.0042,0.9827,0.0878</t>
-  </si>
-  <si>
-    <t>0.0177,0.9689,0.0244,0.0193</t>
-  </si>
-  <si>
-    <t>0.0084,0.9860,0.0101,0.0024</t>
-  </si>
-  <si>
-    <t>0.6189,0.0952,0.1523,0.1659</t>
-  </si>
-  <si>
-    <t>0.5053,0.2476,0.3103,0.0920</t>
-  </si>
-  <si>
-    <t>0.0070,0.0340,0.9776,0.0625</t>
-  </si>
-  <si>
-    <t>0.0135,0.4439,0.9381,0.0046</t>
-  </si>
-  <si>
-    <t>0.0050,0.7539,0.9524,0.0013</t>
-  </si>
-  <si>
-    <t>0.0050,0.9137,0.8535,0.0012</t>
-  </si>
-  <si>
-    <t>0.0048,0.7903,0.9426,0.0022</t>
-  </si>
-  <si>
-    <t>0.0012,0.0016,0.0030,0.9981</t>
-  </si>
-  <si>
-    <t>0.0007,0.0037,0.0007,0.9989</t>
-  </si>
-  <si>
-    <t>0.0005,0.0012,0.0007,0.9992</t>
-  </si>
-  <si>
-    <t>0.0019,0.0048,0.0016,0.9976</t>
-  </si>
-  <si>
-    <t>0.0029,0.0025,0.0039,0.9964</t>
-  </si>
-  <si>
-    <t>0.0008,0.0029,0.0010,0.9988</t>
-  </si>
-  <si>
-    <t>0.0076,0.6216,0.9446,0.0024</t>
-  </si>
-  <si>
-    <t>0.0024,0.7205,0.9825,0.0005</t>
-  </si>
-  <si>
-    <t>0.0065,0.2707,0.9728,0.0041</t>
-  </si>
-  <si>
-    <t>0.0154,0.5860,0.9038,0.0060</t>
-  </si>
-  <si>
-    <t>0.0077,0.7877,0.9179,0.0017</t>
-  </si>
-  <si>
-    <t>0.0097,0.7389,0.9186,0.0046</t>
-  </si>
-  <si>
-    <t>0.9630,0.0132,0.0028,0.0192</t>
-  </si>
-  <si>
-    <t>0.8997,0.0807,0.0058,0.0212</t>
-  </si>
-  <si>
-    <t>0.8738,0.1070,0.0070,0.0245</t>
-  </si>
-  <si>
-    <t>0.9442,0.0252,0.0023,0.0205</t>
-  </si>
-  <si>
-    <t>0.9290,0.0214,0.0029,0.0364</t>
-  </si>
-  <si>
-    <t>0.9335,0.0163,0.0020,0.0358</t>
-  </si>
-  <si>
-    <t>0.9269,0.0152,0.0028,0.0471</t>
-  </si>
-  <si>
-    <t>0.9324,0.0548,0.0082,0.0157</t>
-  </si>
-  <si>
-    <t>0.9383,0.0073,0.0023,0.0545</t>
-  </si>
-  <si>
-    <t>0.9344,0.0239,0.0028,0.0341</t>
-  </si>
-  <si>
-    <t>0.9690,0.0124,0.0026,0.0138</t>
-  </si>
-  <si>
-    <t>0.9559,0.0043,0.0012,0.0409</t>
-  </si>
-  <si>
-    <t>0.9607,0.0268,0.0047,0.0110</t>
-  </si>
-  <si>
-    <t>0.9566,0.0066,0.0015,0.0335</t>
-  </si>
-  <si>
-    <t>0.9059,0.0063,0.0015,0.0992</t>
-  </si>
-  <si>
-    <t>0.9730,0.0066,0.0029,0.0153</t>
-  </si>
-  <si>
-    <t>0.0004,0.0018,0.9893,0.1091</t>
-  </si>
-  <si>
-    <t>0.0542,0.0701,0.8985,0.0607</t>
-  </si>
-  <si>
-    <t>0.2201,0.0167,0.0719,0.6786</t>
-  </si>
-  <si>
-    <t>0.0955,0.0123,0.8689,0.0394</t>
-  </si>
-  <si>
-    <t>0.0205,0.9458,0.0049,0.0899</t>
-  </si>
-  <si>
-    <t>0.0178,0.9620,0.0054,0.0459</t>
-  </si>
-  <si>
-    <t>0.0325,0.9256,0.0071,0.0815</t>
-  </si>
-  <si>
-    <t>0.1973,0.8095,0.0087,0.0243</t>
-  </si>
-  <si>
-    <t>0.0200,0.9577,0.0088,0.0561</t>
-  </si>
-  <si>
-    <t>0.0150,0.9746,0.0073,0.0240</t>
-  </si>
-  <si>
-    <t>0.3441,0.5641,0.0072,0.0622</t>
-  </si>
-  <si>
-    <t>0.0785,0.7438,0.0687,0.3749</t>
-  </si>
-  <si>
-    <t>0.2050,0.0395,0.7135,0.0900</t>
-  </si>
-  <si>
-    <t>0.3715,0.1608,0.1867,0.3710</t>
-  </si>
-  <si>
-    <t>0.2653,0.1409,0.4130,0.3948</t>
-  </si>
-  <si>
-    <t>0.1236,0.1010,0.0743,0.8546</t>
-  </si>
-  <si>
-    <t>0.0066,0.9786,0.0389,0.0347</t>
-  </si>
-  <si>
-    <t>0.0033,0.9851,0.0122,0.0321</t>
-  </si>
-  <si>
-    <t>0.0340,0.9161,0.0434,0.1500</t>
-  </si>
-  <si>
-    <t>0.0048,0.9746,0.2782,0.0219</t>
-  </si>
-  <si>
-    <t>0.1324,0.8762,0.0275,0.0215</t>
-  </si>
-  <si>
-    <t>0.3606,0.6240,0.0173,0.0445</t>
-  </si>
-  <si>
-    <t>0.6734,0.3882,0.0148,0.0229</t>
-  </si>
-  <si>
-    <t>0.8760,0.0104,0.0032,0.1156</t>
-  </si>
-  <si>
-    <t>0.7442,0.0153,0.0057,0.2669</t>
-  </si>
-  <si>
-    <t>0.8944,0.0149,0.0020,0.0737</t>
-  </si>
-  <si>
-    <t>0.8941,0.0686,0.0077,0.0311</t>
-  </si>
-  <si>
-    <t>0.9354,0.0090,0.0019,0.0533</t>
-  </si>
-  <si>
-    <t>0.8614,0.0696,0.0125,0.0524</t>
-  </si>
-  <si>
-    <t>0.9271,0.0314,0.0041,0.0317</t>
-  </si>
-  <si>
-    <t>0.9429,0.0180,0.0057,0.0308</t>
-  </si>
-  <si>
-    <t>0.0179,0.7036,0.8465,0.0120</t>
-  </si>
-  <si>
-    <t>0.0072,0.1878,0.9806,0.0031</t>
-  </si>
-  <si>
-    <t>0.0105,0.0392,0.9714,0.0222</t>
-  </si>
-  <si>
-    <t>0.0050,0.0413,0.9862,0.0102</t>
-  </si>
-  <si>
-    <t>0.1169,0.0667,0.0304,0.8879</t>
-  </si>
-  <si>
-    <t>0.2321,0.0521,0.2917,0.4747</t>
-  </si>
-  <si>
-    <t>0.0898,0.0111,0.4588,0.4618</t>
-  </si>
-  <si>
-    <t>0.5816,0.1898,0.1797,0.0931</t>
-  </si>
-  <si>
-    <t>0.0026,0.0059,0.0032,0.9962</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.0004,0.9998</t>
-  </si>
-  <si>
-    <t>0.0004,0.0018,0.0017,0.9992</t>
-  </si>
-  <si>
-    <t>0.0027,0.0032,0.0021,0.9968</t>
-  </si>
-  <si>
-    <t>0.0051,0.7897,0.9472,0.0018</t>
-  </si>
-  <si>
-    <t>0.6427,0.0397,0.0044,0.2972</t>
-  </si>
-  <si>
-    <t>0.0534,0.6924,0.0118,0.5086</t>
-  </si>
-  <si>
-    <t>0.8260,0.0279,0.0041,0.1463</t>
-  </si>
-  <si>
-    <t>0.5185,0.3914,0.0113,0.0707</t>
-  </si>
-  <si>
-    <t>0.6398,0.0419,0.0143,0.3247</t>
-  </si>
-  <si>
-    <t>0.2231,0.0385,0.0218,0.7947</t>
-  </si>
-  <si>
-    <t>0.6686,0.0068,0.0046,0.3846</t>
-  </si>
-  <si>
-    <t>0.0169,0.1695,0.3585,0.7411</t>
-  </si>
-  <si>
-    <t>0.2110,0.0402,0.0112,0.8154</t>
-  </si>
-  <si>
-    <t>0.4557,0.0221,0.0223,0.5676</t>
-  </si>
-  <si>
-    <t>0.1213,0.5010,0.0126,0.4632</t>
-  </si>
-  <si>
-    <t>0.1461,0.1226,0.0116,0.7984</t>
-  </si>
-  <si>
-    <t>0.6933,0.1665,0.0643,0.0916</t>
-  </si>
-  <si>
-    <t>0.0234,0.6600,0.0137,0.7012</t>
-  </si>
-  <si>
-    <t>0.4623,0.5343,0.0554,0.0638</t>
-  </si>
-  <si>
-    <t>0.1601,0.5454,0.0196,0.3733</t>
-  </si>
-  <si>
-    <t>0.9186,0.0176,0.0036,0.0517</t>
-  </si>
-  <si>
-    <t>0.8342,0.0114,0.0022,0.1674</t>
-  </si>
-  <si>
-    <t>0.9484,0.0170,0.0043,0.0249</t>
-  </si>
-  <si>
-    <t>0.8432,0.0104,0.0045,0.1582</t>
-  </si>
-  <si>
-    <t>0.9140,0.0089,0.0030,0.0775</t>
-  </si>
-  <si>
-    <t>0.9273,0.0199,0.0031,0.0371</t>
-  </si>
-  <si>
-    <t>0.9244,0.0104,0.0027,0.0677</t>
-  </si>
-  <si>
-    <t>0.9241,0.0110,0.0023,0.0554</t>
-  </si>
-  <si>
-    <t>0.1329,0.8110,0.0083,0.0600</t>
-  </si>
-  <si>
-    <t>0.4956,0.5161,0.0116,0.0366</t>
-  </si>
-  <si>
-    <t>0.2419,0.7725,0.0094,0.0319</t>
-  </si>
-  <si>
-    <t>0.0903,0.1163,0.8702,0.0549</t>
-  </si>
-  <si>
-    <t>0.5621,0.0931,0.0032,0.2160</t>
-  </si>
-  <si>
-    <t>0.3696,0.2918,0.0087,0.2333</t>
-  </si>
-  <si>
-    <t>0.8977,0.0458,0.0078,0.0403</t>
-  </si>
-  <si>
-    <t>0.2360,0.5924,0.0177,0.1663</t>
-  </si>
-  <si>
-    <t>0.0031,0.0320,0.9870,0.0282</t>
-  </si>
-  <si>
-    <t>0.5254,0.0920,0.0060,0.3055</t>
-  </si>
-  <si>
-    <t>0.0027,0.0064,0.9694,0.1135</t>
-  </si>
-  <si>
-    <t>0.0042,0.0254,0.9612,0.0854</t>
-  </si>
-  <si>
-    <t>0.0330,0.0166,0.9447,0.0551</t>
-  </si>
-  <si>
-    <t>0.0054,0.0299,0.9739,0.0402</t>
-  </si>
-  <si>
-    <t>0.0274,0.0310,0.9234,0.0612</t>
-  </si>
-  <si>
-    <t>0.0161,0.0062,0.9539,0.0682</t>
-  </si>
-  <si>
-    <t>0.0071,0.0281,0.9773,0.0333</t>
-  </si>
-  <si>
-    <t>0.4762,0.1427,0.2695,0.2180</t>
-  </si>
-  <si>
-    <t>0.2559,0.0368,0.5647,0.1842</t>
-  </si>
-  <si>
-    <t>0.6691,0.1089,0.2181,0.0339</t>
-  </si>
-  <si>
-    <t>0.2083,0.1325,0.7139,0.0799</t>
-  </si>
-  <si>
-    <t>0.3382,0.2305,0.4968,0.0546</t>
-  </si>
-  <si>
-    <t>0.6126,0.0489,0.3593,0.0379</t>
-  </si>
-  <si>
-    <t>0.1530,0.0137,0.0433,0.8439</t>
-  </si>
-  <si>
-    <t>0.6361,0.1584,0.1623,0.0695</t>
-  </si>
-  <si>
-    <t>0.3420,0.6141,0.0082,0.0449</t>
-  </si>
-  <si>
-    <t>0.1980,0.7339,0.0084,0.0547</t>
-  </si>
-  <si>
-    <t>0.4996,0.3755,0.0121,0.0761</t>
-  </si>
-  <si>
-    <t>0.7489,0.1034,0.0045,0.0769</t>
-  </si>
-  <si>
-    <t>0.6057,0.1573,0.0034,0.0977</t>
-  </si>
-  <si>
-    <t>0.3903,0.2528,0.1921,0.2304</t>
-  </si>
-  <si>
-    <t>0.4552,0.0627,0.0924,0.3792</t>
-  </si>
-  <si>
-    <t>0.0129,0.0588,0.0146,0.9777</t>
-  </si>
-  <si>
-    <t>0.3191,0.0356,0.3203,0.2873</t>
-  </si>
-  <si>
-    <t>0.2094,0.0334,0.4924,0.3059</t>
-  </si>
-  <si>
-    <t>0.0088,0.0213,0.9335,0.1838</t>
-  </si>
-  <si>
-    <t>0.0172,0.0449,0.9040,0.1411</t>
-  </si>
-  <si>
-    <t>0.0194,0.0815,0.9523,0.0305</t>
-  </si>
-  <si>
-    <t>0.0166,0.0172,0.8788,0.1687</t>
-  </si>
-  <si>
-    <t>0.0190,0.2559,0.9040,0.0236</t>
-  </si>
-  <si>
-    <t>0.9254,0.0150,0.0033,0.0550</t>
-  </si>
-  <si>
-    <t>0.9312,0.0264,0.0044,0.0350</t>
-  </si>
-  <si>
-    <t>0.7425,0.0297,0.0036,0.2257</t>
-  </si>
-  <si>
-    <t>0.9489,0.0295,0.0064,0.0189</t>
-  </si>
-  <si>
-    <t>0.9378,0.0350,0.0055,0.0221</t>
-  </si>
-  <si>
-    <t>0.8256,0.0716,0.0038,0.0657</t>
-  </si>
-  <si>
-    <t>0.9311,0.0157,0.0023,0.0478</t>
-  </si>
-  <si>
-    <t>0.9331,0.0289,0.0036,0.0287</t>
-  </si>
-  <si>
-    <t>0.0295,0.0651,0.9375,0.0543</t>
-  </si>
-  <si>
-    <t>0.3412,0.4100,0.1634,0.2747</t>
-  </si>
-  <si>
-    <t>0.4042,0.0359,0.0200,0.5762</t>
-  </si>
-  <si>
-    <t>0.0035,0.0131,0.9871,0.0201</t>
-  </si>
-  <si>
-    <t>0.0011,0.0068,0.9896,0.0284</t>
-  </si>
-  <si>
-    <t>0.0306,0.0363,0.9446,0.0293</t>
-  </si>
-  <si>
-    <t>0.0011,0.0024,0.9727,0.1271</t>
-  </si>
-  <si>
-    <t>0.0757,0.0232,0.9079,0.0326</t>
-  </si>
-  <si>
-    <t>0.0003,0.0024,0.9964,0.0200</t>
-  </si>
-  <si>
-    <t>0.0082,0.0086,0.9019,0.2153</t>
-  </si>
-  <si>
-    <t>0.0345,0.0809,0.8786,0.1886</t>
-  </si>
-  <si>
-    <t>0.2820,0.0518,0.2352,0.4840</t>
-  </si>
-  <si>
-    <t>0.1026,0.0116,0.0929,0.8231</t>
-  </si>
-  <si>
-    <t>0.6445,0.0279,0.0770,0.1730</t>
-  </si>
-  <si>
-    <t>0.7254,0.1054,0.0035,0.0846</t>
-  </si>
-  <si>
-    <t>0.9671,0.0155,0.0032,0.0140</t>
-  </si>
-  <si>
-    <t>0.9668,0.0139,0.0031,0.0140</t>
-  </si>
-  <si>
-    <t>0.9271,0.0212,0.0038,0.0370</t>
-  </si>
-  <si>
-    <t>0.7152,0.0659,0.0054,0.1815</t>
-  </si>
-  <si>
-    <t>0.9510,0.0359,0.0053,0.0114</t>
-  </si>
-  <si>
-    <t>0.9494,0.0167,0.0030,0.0282</t>
-  </si>
-  <si>
-    <t>0.7645,0.0739,0.0058,0.1147</t>
-  </si>
-  <si>
-    <t>0.0287,0.3523,0.8640,0.0091</t>
-  </si>
-  <si>
-    <t>0.0031,0.0224,0.9823,0.0406</t>
-  </si>
-  <si>
-    <t>0.0061,0.0397,0.9435,0.1239</t>
-  </si>
-  <si>
-    <t>0.1008,0.0243,0.8557,0.0434</t>
-  </si>
-  <si>
-    <t>0.0045,0.0077,0.9567,0.1148</t>
-  </si>
-  <si>
-    <t>0.0062,0.0063,0.2062,0.9449</t>
-  </si>
-  <si>
-    <t>0.1272,0.0435,0.6820,0.1630</t>
-  </si>
-  <si>
-    <t>0.0120,0.0188,0.6422,0.6483</t>
-  </si>
-  <si>
-    <t>0.0269,0.0082,0.0060,0.9824</t>
-  </si>
-  <si>
-    <t>0.0006,0.0067,0.0011,0.9987</t>
-  </si>
-  <si>
-    <t>0.0027,0.0054,0.0021,0.9965</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.0012,0.9991</t>
-  </si>
-  <si>
-    <t>0.0006,0.0022,0.0007,0.9992</t>
-  </si>
-  <si>
-    <t>0.0343,0.0819,0.0137,0.9606</t>
+    <t>0.0908,0.0721,0.0177,0.9061</t>
+  </si>
+  <si>
+    <t>0.0010,0.0053,0.0014,0.9984</t>
+  </si>
+  <si>
+    <t>0.0695,0.0652,0.0112,0.9326</t>
+  </si>
+  <si>
+    <t>0.0121,0.0270,0.0084,0.9858</t>
+  </si>
+  <si>
+    <t>0.9703,0.0137,0.0029,0.0126</t>
+  </si>
+  <si>
+    <t>0.9458,0.0137,0.0026,0.0330</t>
+  </si>
+  <si>
+    <t>0.9523,0.0303,0.0023,0.0139</t>
+  </si>
+  <si>
+    <t>0.9051,0.0239,0.0031,0.0537</t>
+  </si>
+  <si>
+    <t>0.8741,0.0381,0.0029,0.0593</t>
+  </si>
+  <si>
+    <t>0.9295,0.0226,0.0028,0.0333</t>
+  </si>
+  <si>
+    <t>0.9682,0.0199,0.0033,0.0096</t>
+  </si>
+  <si>
+    <t>0.9537,0.0098,0.0026,0.0349</t>
+  </si>
+  <si>
+    <t>0.2508,0.4007,0.0978,0.3963</t>
+  </si>
+  <si>
+    <t>0.2151,0.0290,0.7404,0.0633</t>
+  </si>
+  <si>
+    <t>0.1672,0.0383,0.7789,0.0902</t>
+  </si>
+  <si>
+    <t>0.0436,0.0344,0.9006,0.1092</t>
+  </si>
+  <si>
+    <t>0.6541,0.0963,0.1454,0.1118</t>
+  </si>
+  <si>
+    <t>0.0234,0.9672,0.0159,0.0203</t>
+  </si>
+  <si>
+    <t>0.0441,0.9451,0.0123,0.0361</t>
+  </si>
+  <si>
+    <t>0.0744,0.8882,0.0129,0.0710</t>
+  </si>
+  <si>
+    <t>0.0318,0.9553,0.0095,0.0333</t>
+  </si>
+  <si>
+    <t>0.0213,0.9695,0.0061,0.0227</t>
+  </si>
+  <si>
+    <t>0.1621,0.0153,0.3395,0.4014</t>
+  </si>
+  <si>
+    <t>0.4091,0.0321,0.4109,0.1268</t>
+  </si>
+  <si>
+    <t>0.0088,0.0082,0.9779,0.0419</t>
+  </si>
+  <si>
+    <t>0.1432,0.0335,0.8100,0.0506</t>
+  </si>
+  <si>
+    <t>0.0200,0.0149,0.9402,0.1033</t>
+  </si>
+  <si>
+    <t>0.0331,0.0073,0.9210,0.0593</t>
+  </si>
+  <si>
+    <t>0.0067,0.0041,0.9694,0.0682</t>
+  </si>
+  <si>
+    <t>0.0439,0.9207,0.0185,0.0796</t>
+  </si>
+  <si>
+    <t>0.4990,0.2746,0.2520,0.0948</t>
+  </si>
+  <si>
+    <t>0.0011,0.0080,0.9916,0.0490</t>
+  </si>
+  <si>
+    <t>0.0243,0.9412,0.0796,0.0543</t>
+  </si>
+  <si>
+    <t>0.5102,0.1129,0.0091,0.2848</t>
+  </si>
+  <si>
+    <t>0.2098,0.2400,0.3724,0.2828</t>
+  </si>
+  <si>
+    <t>0.2972,0.7230,0.0091,0.0275</t>
+  </si>
+  <si>
+    <t>0.0733,0.8917,0.0821,0.0725</t>
+  </si>
+  <si>
+    <t>0.0186,0.5520,0.8928,0.0137</t>
+  </si>
+  <si>
+    <t>0.0109,0.0319,0.8884,0.1875</t>
+  </si>
+  <si>
+    <t>0.0141,0.0294,0.9019,0.1459</t>
+  </si>
+  <si>
+    <t>0.0139,0.0037,0.3878,0.7757</t>
+  </si>
+  <si>
+    <t>0.0349,0.0390,0.9390,0.0224</t>
+  </si>
+  <si>
+    <t>0.0287,0.8887,0.4376,0.0224</t>
+  </si>
+  <si>
+    <t>0.0189,0.0269,0.8388,0.2177</t>
+  </si>
+  <si>
+    <t>0.0212,0.2029,0.0157,0.9511</t>
+  </si>
+  <si>
+    <t>0.0083,0.9630,0.0336,0.1249</t>
+  </si>
+  <si>
+    <t>0.0146,0.9464,0.0493,0.0776</t>
+  </si>
+  <si>
+    <t>0.0079,0.9493,0.0516,0.1306</t>
+  </si>
+  <si>
+    <t>0.0022,0.0214,0.9901,0.0157</t>
+  </si>
+  <si>
+    <t>0.0047,0.1674,0.9881,0.0039</t>
+  </si>
+  <si>
+    <t>0.0246,0.0207,0.9069,0.0918</t>
+  </si>
+  <si>
+    <t>0.0183,0.0104,0.9309,0.0966</t>
+  </si>
+  <si>
+    <t>0.0021,0.0130,0.9890,0.0341</t>
+  </si>
+  <si>
+    <t>0.0067,0.0257,0.9863,0.0094</t>
+  </si>
+  <si>
+    <t>0.9268,0.0423,0.0045,0.0241</t>
+  </si>
+  <si>
+    <t>0.8678,0.0393,0.0084,0.0767</t>
+  </si>
+  <si>
+    <t>0.6230,0.0232,0.0036,0.3931</t>
+  </si>
+  <si>
+    <t>0.0094,0.0557,0.9515,0.1337</t>
+  </si>
+  <si>
+    <t>0.9160,0.0574,0.0067,0.0225</t>
+  </si>
+  <si>
+    <t>0.9591,0.0171,0.0027,0.0166</t>
+  </si>
+  <si>
+    <t>0.9332,0.0407,0.0080,0.0236</t>
+  </si>
+  <si>
+    <t>0.0033,0.8721,0.9487,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.0081,0.9544,0.1808</t>
+  </si>
+  <si>
+    <t>0.0039,0.0166,0.9743,0.0480</t>
+  </si>
+  <si>
+    <t>0.0055,0.6241,0.9699,0.0017</t>
+  </si>
+  <si>
+    <t>0.0019,0.0071,0.9768,0.0830</t>
+  </si>
+  <si>
+    <t>0.0344,0.9349,0.0457,0.0871</t>
+  </si>
+  <si>
+    <t>0.0061,0.9894,0.0188,0.0023</t>
+  </si>
+  <si>
+    <t>0.1605,0.0892,0.7619,0.1645</t>
+  </si>
+  <si>
+    <t>0.5499,0.3976,0.1222,0.0327</t>
+  </si>
+  <si>
+    <t>0.0060,0.0277,0.9884,0.0227</t>
+  </si>
+  <si>
+    <t>0.0056,0.8183,0.9429,0.0015</t>
+  </si>
+  <si>
+    <t>0.0084,0.4184,0.9582,0.0024</t>
+  </si>
+  <si>
+    <t>0.0086,0.8827,0.8349,0.0045</t>
+  </si>
+  <si>
+    <t>0.0096,0.8196,0.8880,0.0026</t>
+  </si>
+  <si>
+    <t>0.0020,0.0031,0.0026,0.9975</t>
+  </si>
+  <si>
+    <t>0.0010,0.0038,0.0016,0.9985</t>
+  </si>
+  <si>
+    <t>0.0014,0.0040,0.0017,0.9979</t>
+  </si>
+  <si>
+    <t>0.0021,0.0027,0.0023,0.9974</t>
+  </si>
+  <si>
+    <t>0.0024,0.0032,0.0096,0.9956</t>
+  </si>
+  <si>
+    <t>0.0006,0.0031,0.0010,0.9990</t>
+  </si>
+  <si>
+    <t>0.0110,0.6861,0.9175,0.0041</t>
+  </si>
+  <si>
+    <t>0.0042,0.7052,0.9724,0.0012</t>
+  </si>
+  <si>
+    <t>0.0171,0.3216,0.9377,0.0137</t>
+  </si>
+  <si>
+    <t>0.0161,0.4519,0.9204,0.0068</t>
+  </si>
+  <si>
+    <t>0.0030,0.3060,0.9839,0.0019</t>
+  </si>
+  <si>
+    <t>0.0108,0.5044,0.9358,0.0042</t>
+  </si>
+  <si>
+    <t>0.9439,0.0270,0.0040,0.0230</t>
+  </si>
+  <si>
+    <t>0.9025,0.0525,0.0049,0.0336</t>
+  </si>
+  <si>
+    <t>0.8936,0.0710,0.0062,0.0286</t>
+  </si>
+  <si>
+    <t>0.9231,0.0171,0.0028,0.0517</t>
+  </si>
+  <si>
+    <t>0.9690,0.0160,0.0039,0.0108</t>
+  </si>
+  <si>
+    <t>0.9617,0.0203,0.0047,0.0135</t>
+  </si>
+  <si>
+    <t>0.8988,0.0116,0.0022,0.0863</t>
+  </si>
+  <si>
+    <t>0.9326,0.0571,0.0062,0.0134</t>
+  </si>
+  <si>
+    <t>0.9580,0.0109,0.0034,0.0263</t>
+  </si>
+  <si>
+    <t>0.9539,0.0066,0.0012,0.0386</t>
+  </si>
+  <si>
+    <t>0.9598,0.0112,0.0025,0.0252</t>
+  </si>
+  <si>
+    <t>0.9249,0.0101,0.0027,0.0670</t>
+  </si>
+  <si>
+    <t>0.9424,0.0176,0.0023,0.0295</t>
+  </si>
+  <si>
+    <t>0.9714,0.0061,0.0017,0.0180</t>
+  </si>
+  <si>
+    <t>0.9113,0.0084,0.0010,0.0823</t>
+  </si>
+  <si>
+    <t>0.9573,0.0080,0.0032,0.0293</t>
+  </si>
+  <si>
+    <t>0.0003,0.0021,0.9947,0.0481</t>
+  </si>
+  <si>
+    <t>0.0680,0.0302,0.8889,0.0602</t>
+  </si>
+  <si>
+    <t>0.1635,0.0123,0.1225,0.6790</t>
+  </si>
+  <si>
+    <t>0.0480,0.0068,0.9554,0.0139</t>
+  </si>
+  <si>
+    <t>0.0177,0.9498,0.0051,0.0917</t>
+  </si>
+  <si>
+    <t>0.0109,0.9711,0.0055,0.0583</t>
+  </si>
+  <si>
+    <t>0.0803,0.8788,0.0067,0.0439</t>
+  </si>
+  <si>
+    <t>0.1119,0.8724,0.0113,0.0315</t>
+  </si>
+  <si>
+    <t>0.0400,0.9324,0.0147,0.0570</t>
+  </si>
+  <si>
+    <t>0.0254,0.9645,0.0084,0.0176</t>
+  </si>
+  <si>
+    <t>0.8308,0.1496,0.0075,0.0236</t>
+  </si>
+  <si>
+    <t>0.4873,0.2631,0.1450,0.1533</t>
+  </si>
+  <si>
+    <t>0.0181,0.0127,0.8844,0.1976</t>
+  </si>
+  <si>
+    <t>0.3606,0.3425,0.2140,0.1816</t>
+  </si>
+  <si>
+    <t>0.3786,0.0392,0.1952,0.3492</t>
+  </si>
+  <si>
+    <t>0.0088,0.0487,0.0062,0.9861</t>
+  </si>
+  <si>
+    <t>0.0140,0.9642,0.0507,0.0486</t>
+  </si>
+  <si>
+    <t>0.0041,0.9733,0.0326,0.0614</t>
+  </si>
+  <si>
+    <t>0.0280,0.9025,0.0376,0.2804</t>
+  </si>
+  <si>
+    <t>0.0068,0.9734,0.2460,0.0153</t>
+  </si>
+  <si>
+    <t>0.1234,0.8880,0.0276,0.0161</t>
+  </si>
+  <si>
+    <t>0.7315,0.2721,0.0132,0.0270</t>
+  </si>
+  <si>
+    <t>0.7184,0.2934,0.0143,0.0337</t>
+  </si>
+  <si>
+    <t>0.9168,0.0313,0.0058,0.0396</t>
+  </si>
+  <si>
+    <t>0.6841,0.0095,0.0030,0.3906</t>
+  </si>
+  <si>
+    <t>0.8199,0.0294,0.0039,0.1315</t>
+  </si>
+  <si>
+    <t>0.8570,0.0505,0.0084,0.0785</t>
+  </si>
+  <si>
+    <t>0.7121,0.0103,0.0016,0.3587</t>
+  </si>
+  <si>
+    <t>0.6816,0.0406,0.0074,0.2642</t>
+  </si>
+  <si>
+    <t>0.9160,0.0399,0.0068,0.0310</t>
+  </si>
+  <si>
+    <t>0.9213,0.0181,0.0065,0.0518</t>
+  </si>
+  <si>
+    <t>0.0295,0.5722,0.8318,0.0158</t>
+  </si>
+  <si>
+    <t>0.0052,0.4083,0.9688,0.0018</t>
+  </si>
+  <si>
+    <t>0.0049,0.0226,0.9807,0.0281</t>
+  </si>
+  <si>
+    <t>0.0096,0.1912,0.9599,0.0128</t>
+  </si>
+  <si>
+    <t>0.0394,0.0736,0.0502,0.9412</t>
+  </si>
+  <si>
+    <t>0.5231,0.1372,0.2802,0.1534</t>
+  </si>
+  <si>
+    <t>0.2450,0.0275,0.3754,0.3327</t>
+  </si>
+  <si>
+    <t>0.3700,0.2548,0.1187,0.3230</t>
+  </si>
+  <si>
+    <t>0.0019,0.0029,0.0014,0.9979</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.0008,0.9997</t>
+  </si>
+  <si>
+    <t>0.0005,0.0044,0.0008,0.9991</t>
+  </si>
+  <si>
+    <t>0.0030,0.0069,0.0028,0.9960</t>
+  </si>
+  <si>
+    <t>0.0040,0.4225,0.9781,0.0031</t>
+  </si>
+  <si>
+    <t>0.8403,0.0250,0.0040,0.1293</t>
+  </si>
+  <si>
+    <t>0.2579,0.3743,0.0161,0.3444</t>
+  </si>
+  <si>
+    <t>0.6227,0.0324,0.0046,0.3513</t>
+  </si>
+  <si>
+    <t>0.7005,0.2895,0.0073,0.0332</t>
+  </si>
+  <si>
+    <t>0.8211,0.0152,0.0086,0.1567</t>
+  </si>
+  <si>
+    <t>0.0160,0.0103,0.0052,0.9864</t>
+  </si>
+  <si>
+    <t>0.7758,0.0301,0.0103,0.1776</t>
+  </si>
+  <si>
+    <t>0.0077,0.0383,0.7440,0.5607</t>
+  </si>
+  <si>
+    <t>0.5400,0.0083,0.0137,0.4861</t>
+  </si>
+  <si>
+    <t>0.5316,0.0113,0.0182,0.4797</t>
+  </si>
+  <si>
+    <t>0.0875,0.8741,0.0144,0.0744</t>
+  </si>
+  <si>
+    <t>0.4444,0.2331,0.0230,0.2772</t>
+  </si>
+  <si>
+    <t>0.4902,0.4899,0.0314,0.0581</t>
+  </si>
+  <si>
+    <t>0.0199,0.7134,0.0125,0.6455</t>
+  </si>
+  <si>
+    <t>0.3230,0.5973,0.0536,0.1354</t>
+  </si>
+  <si>
+    <t>0.1814,0.7646,0.0249,0.0959</t>
+  </si>
+  <si>
+    <t>0.8857,0.0412,0.0043,0.0482</t>
+  </si>
+  <si>
+    <t>0.8676,0.0212,0.0036,0.0977</t>
+  </si>
+  <si>
+    <t>0.9259,0.0254,0.0045,0.0369</t>
+  </si>
+  <si>
+    <t>0.8055,0.0247,0.0075,0.1502</t>
+  </si>
+  <si>
+    <t>0.9532,0.0066,0.0025,0.0390</t>
+  </si>
+  <si>
+    <t>0.8525,0.0397,0.0058,0.0836</t>
+  </si>
+  <si>
+    <t>0.8769,0.0294,0.0046,0.0796</t>
+  </si>
+  <si>
+    <t>0.8742,0.0128,0.0028,0.1133</t>
+  </si>
+  <si>
+    <t>0.1237,0.7841,0.0073,0.0784</t>
+  </si>
+  <si>
+    <t>0.2211,0.6817,0.0157,0.1038</t>
+  </si>
+  <si>
+    <t>0.2352,0.7095,0.0110,0.0643</t>
+  </si>
+  <si>
+    <t>0.0808,0.0788,0.8769,0.0588</t>
+  </si>
+  <si>
+    <t>0.9089,0.0354,0.0041,0.0397</t>
+  </si>
+  <si>
+    <t>0.5208,0.2961,0.0142,0.1282</t>
+  </si>
+  <si>
+    <t>0.4451,0.1865,0.0063,0.2381</t>
+  </si>
+  <si>
+    <t>0.6964,0.2422,0.0074,0.0496</t>
+  </si>
+  <si>
+    <t>0.0034,0.0163,0.9880,0.0340</t>
+  </si>
+  <si>
+    <t>0.8279,0.0606,0.0063,0.0792</t>
+  </si>
+  <si>
+    <t>0.0071,0.0076,0.9525,0.0962</t>
+  </si>
+  <si>
+    <t>0.0024,0.0254,0.9701,0.0775</t>
+  </si>
+  <si>
+    <t>0.0146,0.0101,0.9151,0.1995</t>
+  </si>
+  <si>
+    <t>0.0039,0.0425,0.9782,0.0393</t>
+  </si>
+  <si>
+    <t>0.0100,0.0148,0.9627,0.0547</t>
+  </si>
+  <si>
+    <t>0.0138,0.0048,0.9550,0.0582</t>
+  </si>
+  <si>
+    <t>0.0245,0.0367,0.9406,0.0563</t>
+  </si>
+  <si>
+    <t>0.3235,0.0460,0.5926,0.1203</t>
+  </si>
+  <si>
+    <t>0.4282,0.0455,0.5094,0.0772</t>
+  </si>
+  <si>
+    <t>0.5103,0.1495,0.2902,0.1397</t>
+  </si>
+  <si>
+    <t>0.1995,0.1163,0.7350,0.0479</t>
+  </si>
+  <si>
+    <t>0.4116,0.0885,0.5610,0.0296</t>
+  </si>
+  <si>
+    <t>0.5965,0.0540,0.3463,0.0560</t>
+  </si>
+  <si>
+    <t>0.3769,0.1127,0.2055,0.3521</t>
+  </si>
+  <si>
+    <t>0.6184,0.0564,0.3394,0.0437</t>
+  </si>
+  <si>
+    <t>0.2184,0.5998,0.0075,0.1230</t>
+  </si>
+  <si>
+    <t>0.1351,0.8548,0.0095,0.0310</t>
+  </si>
+  <si>
+    <t>0.2993,0.6638,0.0091,0.0448</t>
+  </si>
+  <si>
+    <t>0.7267,0.1678,0.0083,0.0623</t>
+  </si>
+  <si>
+    <t>0.5981,0.4175,0.0083,0.0289</t>
+  </si>
+  <si>
+    <t>0.5926,0.1027,0.2180,0.1309</t>
+  </si>
+  <si>
+    <t>0.5812,0.1326,0.0918,0.1709</t>
+  </si>
+  <si>
+    <t>0.0395,0.0891,0.0401,0.9400</t>
+  </si>
+  <si>
+    <t>0.1175,0.1017,0.1073,0.8352</t>
+  </si>
+  <si>
+    <t>0.0860,0.0630,0.0607,0.9046</t>
+  </si>
+  <si>
+    <t>0.0072,0.0100,0.7759,0.6174</t>
+  </si>
+  <si>
+    <t>0.0239,0.0642,0.8601,0.1751</t>
+  </si>
+  <si>
+    <t>0.0244,0.1142,0.8892,0.0904</t>
+  </si>
+  <si>
+    <t>0.0346,0.0744,0.9051,0.0676</t>
+  </si>
+  <si>
+    <t>0.0336,0.4206,0.8582,0.0175</t>
+  </si>
+  <si>
+    <t>0.8171,0.0770,0.0053,0.0728</t>
+  </si>
+  <si>
+    <t>0.9543,0.0183,0.0038,0.0197</t>
+  </si>
+  <si>
+    <t>0.8913,0.0178,0.0020,0.0814</t>
+  </si>
+  <si>
+    <t>0.9142,0.0706,0.0052,0.0178</t>
+  </si>
+  <si>
+    <t>0.9363,0.0295,0.0059,0.0257</t>
+  </si>
+  <si>
+    <t>0.9444,0.0368,0.0046,0.0176</t>
+  </si>
+  <si>
+    <t>0.9381,0.0208,0.0027,0.0321</t>
+  </si>
+  <si>
+    <t>0.8990,0.0340,0.0067,0.0556</t>
+  </si>
+  <si>
+    <t>0.0332,0.0353,0.9487,0.0435</t>
+  </si>
+  <si>
+    <t>0.5259,0.3012,0.1979,0.1201</t>
+  </si>
+  <si>
+    <t>0.2612,0.0415,0.0173,0.7761</t>
+  </si>
+  <si>
+    <t>0.0049,0.0140,0.9918,0.0081</t>
+  </si>
+  <si>
+    <t>0.0005,0.0032,0.9795,0.1069</t>
+  </si>
+  <si>
+    <t>0.0906,0.1579,0.8072,0.0332</t>
+  </si>
+  <si>
+    <t>0.0010,0.0041,0.9810,0.0764</t>
+  </si>
+  <si>
+    <t>0.0444,0.0234,0.9278,0.0344</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9968,0.0333</t>
+  </si>
+  <si>
+    <t>0.0095,0.0177,0.9601,0.0504</t>
+  </si>
+  <si>
+    <t>0.1095,0.0822,0.8355,0.0582</t>
+  </si>
+  <si>
+    <t>0.5411,0.2158,0.2164,0.0629</t>
+  </si>
+  <si>
+    <t>0.4502,0.0180,0.2059,0.2264</t>
+  </si>
+  <si>
+    <t>0.1088,0.0909,0.0723,0.8685</t>
+  </si>
+  <si>
+    <t>0.7975,0.1338,0.0065,0.0432</t>
+  </si>
+  <si>
+    <t>0.9219,0.0200,0.0025,0.0425</t>
+  </si>
+  <si>
+    <t>0.8641,0.0129,0.0026,0.1220</t>
+  </si>
+  <si>
+    <t>0.9597,0.0186,0.0032,0.0153</t>
+  </si>
+  <si>
+    <t>0.8020,0.0695,0.0041,0.0751</t>
+  </si>
+  <si>
+    <t>0.9347,0.0172,0.0038,0.0370</t>
+  </si>
+  <si>
+    <t>0.9569,0.0381,0.0046,0.0084</t>
+  </si>
+  <si>
+    <t>0.9163,0.0368,0.0049,0.0379</t>
+  </si>
+  <si>
+    <t>0.0708,0.0390,0.8427,0.0934</t>
+  </si>
+  <si>
+    <t>0.0100,0.0296,0.9648,0.0477</t>
+  </si>
+  <si>
+    <t>0.0021,0.0079,0.9629,0.1419</t>
+  </si>
+  <si>
+    <t>0.1111,0.0295,0.8259,0.0731</t>
+  </si>
+  <si>
+    <t>0.0082,0.0150,0.9559,0.0959</t>
+  </si>
+  <si>
+    <t>0.0159,0.0084,0.6364,0.6612</t>
+  </si>
+  <si>
+    <t>0.1253,0.1742,0.7393,0.0752</t>
+  </si>
+  <si>
+    <t>0.0152,0.0314,0.4825,0.7399</t>
+  </si>
+  <si>
+    <t>0.0916,0.0298,0.0065,0.9396</t>
+  </si>
+  <si>
+    <t>0.0005,0.0067,0.0009,0.9989</t>
+  </si>
+  <si>
+    <t>0.0014,0.0059,0.0010,0.9980</t>
+  </si>
+  <si>
+    <t>0.0009,0.0023,0.0014,0.9987</t>
+  </si>
+  <si>
+    <t>0.0003,0.0009,0.0006,0.9995</t>
+  </si>
+  <si>
+    <t>0.0168,0.0473,0.0095,0.9795</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1965,7 @@
         <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1990,7 +1993,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2158,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2270,7 +2273,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2368,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2410,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2494,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2508,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2578,7 +2581,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2648,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2704,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2928,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,7 +2987,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3124,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3166,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3435,7 @@
         <v>260</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3572,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3852,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,10 +4118,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,10 +4146,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4160,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,10 +4174,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,10 +4188,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4219,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4233,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4356,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4370,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4384,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4398,7 +4401,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,10 +4440,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,10 +4454,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4622,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4636,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4664,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4706,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4807,7 @@
         <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,10 +4846,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4902,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5042,7 +5045,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5059,7 @@
         <v>260</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5168,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5182,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,10 +5210,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,10 +5434,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5451,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5521,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
